--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>us-en/desktops.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>us-en/desktops</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>category-landing</t>
+  </si>
+  <si>
+    <t>2026-04-08T12:05:27.174Z</t>
+  </si>
+  <si>
+    <t>desktops | HP® Official Site</t>
+  </si>
+  <si>
+    <t>https://www.hp.com/us-en/desktops.html</t>
+  </si>
+  <si>
     <t>us-en/home.report.json</t>
   </si>
   <si>
@@ -46,19 +70,121 @@
     <t>us-en/home</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-08T00:33:46.325Z</t>
+    <t>2026-04-08T12:07:29.131Z</t>
   </si>
   <si>
     <t>Laptop Computers, Desktops, Printers, Ink &amp; Toner | HP® Official Site</t>
   </si>
   <si>
     <t>https://www.hp.com/us-en/home.html</t>
+  </si>
+  <si>
+    <t>us-en/laptops-and-2-in-1s.report.json</t>
+  </si>
+  <si>
+    <t>["cards","cards","carousel","accordion"]</t>
+  </si>
+  <si>
+    <t>us-en/laptops-and-2-in-1s</t>
+  </si>
+  <si>
+    <t>2026-04-08T12:05:21.483Z</t>
+  </si>
+  <si>
+    <t>HP Laptop Computers and 2-in-1 PCs | HP® Official Site</t>
+  </si>
+  <si>
+    <t>https://www.hp.com/us-en/laptops-and-2-in-1s.html</t>
+  </si>
+  <si>
+    <t>us-en/printers.report.json</t>
+  </si>
+  <si>
+    <t>us-en/printers</t>
+  </si>
+  <si>
+    <t>2026-04-08T12:05:37.569Z</t>
+  </si>
+  <si>
+    <t>printers | HP® Official Site</t>
+  </si>
+  <si>
+    <t>https://www.hp.com/us-en/printers.html</t>
+  </si>
+  <si>
+    <t>us-en/sustainable-impact.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","cards","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>us-en/sustainable-impact</t>
+  </si>
+  <si>
+    <t>content-editorial</t>
+  </si>
+  <si>
+    <t>2026-04-08T12:06:12.929Z</t>
+  </si>
+  <si>
+    <t>Sustainable Impact | HP® Official Site</t>
+  </si>
+  <si>
+    <t>https://www.hp.com/us-en/sustainable-impact.html</t>
+  </si>
+  <si>
+    <t>us-en/all-in-plan/printers.report.json</t>
+  </si>
+  <si>
+    <t>us-en/all-in-plan/printers</t>
+  </si>
+  <si>
+    <t>product-marketing</t>
+  </si>
+  <si>
+    <t>2026-04-08T12:06:08.312Z</t>
+  </si>
+  <si>
+    <t>HP All-In Plan – Printer Plans | HP® Official Site</t>
+  </si>
+  <si>
+    <t>https://www.hp.com/us-en/all-in-plan/printers.html</t>
+  </si>
+  <si>
+    <t>us-en/printers/smart-tank.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","cards","cards","cards","cards","cards","columns","accordion","accordion","accordion","accordion","accordion","accordion","accordion","accordion","accordion"]</t>
+  </si>
+  <si>
+    <t>us-en/printers/smart-tank</t>
+  </si>
+  <si>
+    <t>2026-04-08T12:05:43.806Z</t>
+  </si>
+  <si>
+    <t>HP Smart Tank Printers – Refillable Ink Tank Printers | HP® Official Site</t>
+  </si>
+  <si>
+    <t>https://www.hp.com/us-en/printers/smart-tank.html</t>
+  </si>
+  <si>
+    <t>us-en/software/microsoft-copilot-pcs-for-home.report.json</t>
+  </si>
+  <si>
+    <t>us-en/software/microsoft-copilot-pcs-for-home</t>
+  </si>
+  <si>
+    <t>2026-04-08T12:05:55.964Z</t>
+  </si>
+  <si>
+    <t>Microsoft Copilot+ PCs For Home | HP® Official Site</t>
+  </si>
+  <si>
+    <t>https://www.hp.com/us-en/software/microsoft-copilot-pcs-for-home.html</t>
   </si>
 </sst>
 </file>
@@ -447,16 +573,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +633,188 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>category-landing</t>
   </si>
   <si>
-    <t>2026-04-08T12:05:27.174Z</t>
+    <t>2026-04-08T12:08:18.633Z</t>
   </si>
   <si>
     <t>desktops | HP® Official Site</t>
@@ -64,7 +64,7 @@
     <t>us-en/home.report.json</t>
   </si>
   <si>
-    <t>["carousel","cards","cards","cards","cards","cards","hero","hero","hero","hero","columns"]</t>
+    <t>["carousel","icon-grid","product-card","cards","cards","cards","hero","hero","hero","hero","columns"]</t>
   </si>
   <si>
     <t>us-en/home</t>
@@ -73,7 +73,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-08T12:07:29.131Z</t>
+    <t>2026-04-08T12:26:47.046Z</t>
   </si>
   <si>
     <t>Laptop Computers, Desktops, Printers, Ink &amp; Toner | HP® Official Site</t>
@@ -91,7 +91,7 @@
     <t>us-en/laptops-and-2-in-1s</t>
   </si>
   <si>
-    <t>2026-04-08T12:05:21.483Z</t>
+    <t>2026-04-08T12:08:08.991Z</t>
   </si>
   <si>
     <t>HP Laptop Computers and 2-in-1 PCs | HP® Official Site</t>
@@ -106,7 +106,7 @@
     <t>us-en/printers</t>
   </si>
   <si>
-    <t>2026-04-08T12:05:37.569Z</t>
+    <t>2026-04-08T12:08:28.718Z</t>
   </si>
   <si>
     <t>printers | HP® Official Site</t>
@@ -127,7 +127,7 @@
     <t>content-editorial</t>
   </si>
   <si>
-    <t>2026-04-08T12:06:12.929Z</t>
+    <t>2026-04-08T12:09:08.199Z</t>
   </si>
   <si>
     <t>Sustainable Impact | HP® Official Site</t>
@@ -145,7 +145,7 @@
     <t>product-marketing</t>
   </si>
   <si>
-    <t>2026-04-08T12:06:08.312Z</t>
+    <t>2026-04-08T12:09:02.452Z</t>
   </si>
   <si>
     <t>HP All-In Plan – Printer Plans | HP® Official Site</t>
@@ -163,7 +163,7 @@
     <t>us-en/printers/smart-tank</t>
   </si>
   <si>
-    <t>2026-04-08T12:05:43.806Z</t>
+    <t>2026-04-08T12:08:35.769Z</t>
   </si>
   <si>
     <t>HP Smart Tank Printers – Refillable Ink Tank Printers | HP® Official Site</t>
@@ -178,7 +178,7 @@
     <t>us-en/software/microsoft-copilot-pcs-for-home</t>
   </si>
   <si>
-    <t>2026-04-08T12:05:55.964Z</t>
+    <t>2026-04-08T12:08:49.469Z</t>
   </si>
   <si>
     <t>Microsoft Copilot+ PCs For Home | HP® Official Site</t>
